--- a/excels/Originals/9_asses.masses_E9Proxy.xlsx
+++ b/excels/Originals/9_asses.masses_E9Proxy.xlsx
@@ -566,7 +566,7 @@
     <t>Sonunda Teknopol Büyükşehir'e gidebilirim!</t>
   </si>
   <si>
-    <t>'k Kan eindelijk naar Mechalen!</t>
+    <t>'k Kan eindelijk naar Technopolis!</t>
   </si>
   <si>
     <t>Per fi puc anar a Tecnolona!</t>
@@ -698,7 +698,7 @@
     <t>Kuyu Bozuk Dayı... Eşek olmak o kadar korkunç bir şey mi?</t>
   </si>
   <si>
-    <t>Oom Stoere—Piet... is het zo erg om een ezel te zijn?</t>
+    <t>Nonkel Stoere—Piet... is het zo erg om een ezel te zijn?</t>
   </si>
   <si>
     <t>Oncle Rudase—Jofre... és tan terrible com dius, ser un ruc?</t>
@@ -995,7 +995,7 @@
     <t>Teknopol Büyükşehir'e mi gidiyorsun şimdi?</t>
   </si>
   <si>
-    <t>Ga je nu naar Mechalen...?</t>
+    <t>Ga je nu naar Technopolis...?</t>
   </si>
   <si>
     <t>I ara ja te'n vas a Tecnolona...?</t>
@@ -1166,7 +1166,7 @@
     <t>Ben de Teknopol Büyükşehir'i görmek istiyorum! Birlikte gidebiliriz!</t>
   </si>
   <si>
-    <t>Maar ik wil Mechalen ook zien! We kunnen samen gaan!</t>
+    <t>Maar ik wil Technopolis ook zien! We kunnen samen gaan!</t>
   </si>
   <si>
     <t>Però jo també vull veure Tecnolona!\nHi podem anar junts!</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">Senin Bozuk Dayı'n bir Eşek, ruhsuz, şeytan ve çocuk katili bir Makine değil. </t>
   </si>
   <si>
-    <t>Je Oom Stoere is een Ezel, niet een slechte, zielloze, kind-dodende Machine.</t>
+    <t>Je Nonkel Stoere is een Ezel, niet een slechte, zielloze, kind-dodende Machine.</t>
   </si>
   <si>
     <t>L'Oncle Rudase és un Ase, no una Màquina malvada, inanimada, infanticida.</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">Ama aslında, Tanrılar beni bir eşeğe çevirdi. </t>
   </si>
   <si>
-    <t>Terwijl in werkelijkheid DE GODEN mij in nen Ezel hadden veranderd.</t>
+    <t>Terwijl in werkelijkheid de Goden mij in nen Ezel hadden veranderd.</t>
   </si>
   <si>
     <t>En realitat, els Déus em van transformar en un ruc.</t>
@@ -4904,7 +4904,7 @@
     <t>Bu da dayım. O da bir Makine!</t>
   </si>
   <si>
-    <t>Dit is mijn nonkel. Hij is ook een Machine!</t>
+    <t>Dit is mijn Nonkel. Hij is ook een Machine!</t>
   </si>
   <si>
     <t>Aquest és el meu Oncle. Ell també és una Màquina!</t>
@@ -6464,7 +6464,7 @@
     <t>Peygamber olursan, tarihe ilk Peygamber-Makine olarak geçeceksin.</t>
   </si>
   <si>
-    <t>Als de Profeet zult gij de Geschiedenis ingaan als de eerste Profetische Machine.</t>
+    <t>Als de Profeet zult gij de Geschiedenis ingaan als de eerste Profeet-Machine.</t>
   </si>
   <si>
     <t>Com a Profeta, passaràs a la Història com la primera Màquina-Profeta.</t>
@@ -6872,7 +6872,7 @@
     <t>İlk durağım Teknopol Büyükşehir olabiliyor mu?</t>
   </si>
   <si>
-    <t>Kan de eerste stop Mechalen zijn?</t>
+    <t>Kan de eerste stop Technopolis zijn?</t>
   </si>
   <si>
     <t>Podem començar per Tecnolona?</t>
@@ -7112,7 +7112,7 @@
     <t>Hasta Altın Tanrı Teyzeler, ben de Devrim Rüzgarları üzerinde uçabilir miyim?</t>
   </si>
   <si>
-    <t>Tante Snot—Gouden—Goden, mag ik ook op de Winden van de Revolutie vliegen?</t>
+    <t>Tante Snot—Gouden—Goden, mag ik ook op de Winden der Revolutie vliegen?</t>
   </si>
   <si>
     <t>Tieta Feblase—Ase d'Or—Déus, puc solcar els Vents de la Revolució també?</t>
@@ -7250,7 +7250,7 @@
     <t xml:space="preserve">Teknopol Büyükşehir'de görüşürüz. </t>
   </si>
   <si>
-    <t>'k Zie u in Mechalen.</t>
+    <t>'k Zie u in Technopolis.</t>
   </si>
   <si>
     <t>Ens veiem a Tecnolona.</t>
@@ -7556,7 +7556,7 @@
     <t>Benimle Teknopol Büyükşehir'e gelir misin?</t>
   </si>
   <si>
-    <t>Wil je met mij mee naar Mechalen?</t>
+    <t>Wil je met mij mee naar Technopolis?</t>
   </si>
   <si>
     <t>M'acompanyes a Tecnolona?</t>
@@ -7706,7 +7706,7 @@
     <t>Sırtımıza atla ve Devrim Rüzgarları üzerinde uçalım!</t>
   </si>
   <si>
-    <t>Klim op onze rug en laat ons vliegen op de Wind der Revolutie!</t>
+    <t>Klim op onze rug en laat ons vliegen op de Winden der Revolutie!</t>
   </si>
   <si>
     <t>Enfila't a la nostra espatlla i solquem els Vents de la Revolució!</t>
@@ -8198,7 +8198,7 @@
     <t xml:space="preserve">Ben gelir bulurum seni Teknopol'de. </t>
   </si>
   <si>
-    <t>'k Kom u zoeken in Mechalen.</t>
+    <t>'k Kom u zoeken in Technopolis.</t>
   </si>
   <si>
     <t>Vindré a buscar-te a Tecnolona.</t>
@@ -8612,7 +8612,7 @@
     <t xml:space="preserve">Ben Teknopol Büyükşehir'e gidiyorum. </t>
   </si>
   <si>
-    <t>'k Ga naar Mechalen.</t>
+    <t>'k Ga naar Technopolis.</t>
   </si>
   <si>
     <t>Me'n vaig a Tecnolona.</t>
